--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6690" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6690" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -835,6 +835,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Supply.statusCode</t>
@@ -8222,7 +8226,7 @@
         <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>74</v>
+        <v>268</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>74</v>
@@ -8230,10 +8234,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8289,25 +8293,25 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8327,10 +8331,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8353,7 +8357,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -8406,7 +8410,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8426,10 +8430,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8452,7 +8456,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8485,7 +8489,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8503,7 +8507,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8523,10 +8527,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8549,7 +8553,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8602,7 +8606,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8622,10 +8626,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8648,7 +8652,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8701,7 +8705,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8721,10 +8725,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8747,13 +8751,13 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8804,7 +8808,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8824,10 +8828,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8850,7 +8854,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8903,7 +8907,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8923,10 +8927,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8949,13 +8953,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9006,7 +9010,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -9026,10 +9030,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9127,10 +9131,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9228,10 +9232,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9329,10 +9333,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9430,10 +9434,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9533,10 +9537,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9636,10 +9640,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9739,10 +9743,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9842,10 +9846,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9943,10 +9947,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9980,7 +9984,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>74</v>
@@ -10002,7 +10006,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -10020,7 +10024,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -10040,10 +10044,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10066,7 +10070,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -10119,7 +10123,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -10139,10 +10143,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10165,7 +10169,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -10218,7 +10222,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10238,10 +10242,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10264,7 +10268,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -10317,7 +10321,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10337,10 +10341,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10363,7 +10367,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10416,7 +10420,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10436,10 +10440,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10462,7 +10466,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10515,7 +10519,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10535,10 +10539,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10561,7 +10565,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10614,7 +10618,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10634,10 +10638,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10660,7 +10664,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10713,7 +10717,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10733,10 +10737,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10759,7 +10763,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10800,7 +10804,7 @@
         <v>74</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
@@ -10810,7 +10814,7 @@
         <v>124</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10830,13 +10834,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>74</v>
@@ -10858,13 +10862,13 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10915,7 +10919,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10935,10 +10939,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11036,10 +11040,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11137,10 +11141,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11238,10 +11242,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11339,10 +11343,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11442,10 +11446,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11545,10 +11549,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11648,10 +11652,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11751,10 +11755,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11852,10 +11856,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11892,7 +11896,7 @@
         <v>74</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>74</v>
@@ -11911,7 +11915,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11929,7 +11933,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -11949,10 +11953,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11979,7 +11983,7 @@
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -12030,7 +12034,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -12050,10 +12054,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12080,12 +12084,12 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
@@ -12131,7 +12135,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -12151,10 +12155,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12230,7 +12234,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -12250,10 +12254,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12276,7 +12280,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12329,7 +12333,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12349,10 +12353,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12375,7 +12379,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12428,7 +12432,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12448,10 +12452,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12474,7 +12478,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12527,7 +12531,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12547,10 +12551,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12573,7 +12577,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12626,7 +12630,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12646,10 +12650,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12672,7 +12676,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12725,7 +12729,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12745,10 +12749,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12771,7 +12775,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12824,7 +12828,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12844,10 +12848,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12870,7 +12874,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12923,7 +12927,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12943,10 +12947,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12969,7 +12973,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13022,7 +13026,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13042,10 +13046,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13068,7 +13072,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -13121,7 +13125,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13141,10 +13145,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13167,7 +13171,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13220,7 +13224,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13240,10 +13244,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13266,7 +13270,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13319,7 +13323,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13339,13 +13343,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>74</v>
@@ -13367,13 +13371,13 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13424,7 +13428,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13444,10 +13448,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13545,10 +13549,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13646,10 +13650,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13747,10 +13751,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13848,10 +13852,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13951,10 +13955,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14054,10 +14058,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14157,10 +14161,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14260,10 +14264,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14361,10 +14365,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14401,7 +14405,7 @@
         <v>74</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>74</v>
@@ -14420,7 +14424,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -14438,7 +14442,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -14458,10 +14462,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14488,7 +14492,7 @@
       </c>
       <c r="L124" s="2"/>
       <c r="M124" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14539,7 +14543,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14559,10 +14563,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14589,12 +14593,12 @@
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
@@ -14640,7 +14644,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14660,10 +14664,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14739,7 +14743,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14759,10 +14763,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14785,7 +14789,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14838,7 +14842,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14858,10 +14862,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14884,7 +14888,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14937,7 +14941,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14957,10 +14961,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14983,7 +14987,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -15036,7 +15040,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -15056,10 +15060,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15082,7 +15086,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15135,7 +15139,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15155,10 +15159,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15181,7 +15185,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15234,7 +15238,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15254,10 +15258,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15280,7 +15284,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15333,7 +15337,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15353,10 +15357,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15379,7 +15383,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15432,7 +15436,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15452,10 +15456,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15478,7 +15482,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15531,7 +15535,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15551,10 +15555,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15577,7 +15581,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15630,7 +15634,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15650,10 +15654,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15676,7 +15680,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15729,7 +15733,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15749,10 +15753,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15775,7 +15779,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15828,7 +15832,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15848,13 +15852,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>74</v>
@@ -15876,13 +15880,13 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -15933,7 +15937,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15953,10 +15957,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16054,10 +16058,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16155,10 +16159,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16256,10 +16260,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16357,10 +16361,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16460,10 +16464,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16563,10 +16567,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16666,10 +16670,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16769,10 +16773,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16870,10 +16874,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16910,7 +16914,7 @@
         <v>74</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>74</v>
@@ -16929,7 +16933,7 @@
       </c>
       <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -16947,7 +16951,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -16967,10 +16971,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16997,7 +17001,7 @@
       </c>
       <c r="L149" s="2"/>
       <c r="M149" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -17009,7 +17013,7 @@
         <v>74</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>74</v>
@@ -17048,7 +17052,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -17068,10 +17072,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17098,12 +17102,12 @@
       </c>
       <c r="L150" s="2"/>
       <c r="M150" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
@@ -17149,7 +17153,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17169,10 +17173,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17248,7 +17252,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17268,10 +17272,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17294,7 +17298,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17347,7 +17351,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17367,10 +17371,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17393,7 +17397,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17446,7 +17450,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17466,10 +17470,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17492,7 +17496,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17545,7 +17549,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17565,10 +17569,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17591,7 +17595,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17644,7 +17648,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17664,10 +17668,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17690,7 +17694,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17743,7 +17747,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17763,10 +17767,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17789,7 +17793,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17842,7 +17846,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17862,10 +17866,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17888,7 +17892,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17941,7 +17945,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17961,10 +17965,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17987,7 +17991,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18040,7 +18044,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18060,10 +18064,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18086,7 +18090,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18139,7 +18143,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18159,10 +18163,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18185,7 +18189,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18238,7 +18242,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18258,10 +18262,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18284,7 +18288,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18337,7 +18341,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18357,13 +18361,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>74</v>
@@ -18385,13 +18389,13 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18442,7 +18446,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18462,10 +18466,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18563,10 +18567,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18664,10 +18668,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18765,10 +18769,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18866,10 +18870,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18969,10 +18973,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19072,10 +19076,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19175,10 +19179,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19278,10 +19282,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19379,10 +19383,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19419,7 +19423,7 @@
         <v>74</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>74</v>
@@ -19438,7 +19442,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>74</v>
@@ -19456,7 +19460,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -19476,10 +19480,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19506,7 +19510,7 @@
       </c>
       <c r="L174" s="2"/>
       <c r="M174" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19518,7 +19522,7 @@
         <v>74</v>
       </c>
       <c r="S174" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T174" t="s" s="2">
         <v>74</v>
@@ -19557,7 +19561,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -19577,10 +19581,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19607,12 +19611,12 @@
       </c>
       <c r="L175" s="2"/>
       <c r="M175" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
@@ -19658,7 +19662,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -19678,10 +19682,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19757,7 +19761,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -19777,10 +19781,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19803,7 +19807,7 @@
         <v>74</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -19856,7 +19860,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -19876,10 +19880,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19902,7 +19906,7 @@
         <v>74</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -19955,7 +19959,7 @@
         <v>74</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -19975,10 +19979,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20001,7 +20005,7 @@
         <v>74</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20054,7 +20058,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -20074,10 +20078,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20100,7 +20104,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20153,7 +20157,7 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -20173,10 +20177,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20199,7 +20203,7 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
@@ -20252,7 +20256,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -20272,10 +20276,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20298,7 +20302,7 @@
         <v>74</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
@@ -20351,7 +20355,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -20371,10 +20375,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20397,7 +20401,7 @@
         <v>74</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -20450,7 +20454,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20470,10 +20474,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20496,7 +20500,7 @@
         <v>74</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -20549,7 +20553,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20569,10 +20573,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20595,7 +20599,7 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -20648,7 +20652,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -20668,10 +20672,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20694,7 +20698,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -20747,7 +20751,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -20767,10 +20771,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20793,7 +20797,7 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -20846,7 +20850,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -20866,13 +20870,13 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D188" t="s" s="2">
         <v>74</v>
@@ -20894,13 +20898,13 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -20951,7 +20955,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -20971,10 +20975,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21072,10 +21076,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21173,10 +21177,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21274,10 +21278,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21375,10 +21379,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21478,10 +21482,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21581,10 +21585,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21684,10 +21688,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21787,10 +21791,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -21888,10 +21892,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -21928,7 +21932,7 @@
         <v>74</v>
       </c>
       <c r="S198" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="T198" t="s" s="2">
         <v>74</v>
@@ -21947,7 +21951,7 @@
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>74</v>
@@ -21965,7 +21969,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>75</v>
@@ -21985,10 +21989,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22015,7 +22019,7 @@
       </c>
       <c r="L199" s="2"/>
       <c r="M199" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -22066,7 +22070,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22086,10 +22090,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22116,12 +22120,12 @@
       </c>
       <c r="L200" s="2"/>
       <c r="M200" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
@@ -22167,7 +22171,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22187,10 +22191,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22266,7 +22270,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22286,10 +22290,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22312,7 +22316,7 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22365,7 +22369,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -22385,10 +22389,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22411,7 +22415,7 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22464,7 +22468,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -22484,10 +22488,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22510,7 +22514,7 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -22563,7 +22567,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -22583,10 +22587,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22609,7 +22613,7 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -22662,7 +22666,7 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -22682,10 +22686,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -22708,7 +22712,7 @@
         <v>74</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
@@ -22761,7 +22765,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -22781,10 +22785,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -22807,7 +22811,7 @@
         <v>74</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
@@ -22860,7 +22864,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -22880,10 +22884,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -22906,7 +22910,7 @@
         <v>74</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
@@ -22959,7 +22963,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -22979,10 +22983,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23005,7 +23009,7 @@
         <v>74</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -23058,7 +23062,7 @@
         <v>74</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -23078,10 +23082,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23104,7 +23108,7 @@
         <v>74</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23157,7 +23161,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23177,10 +23181,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23203,7 +23207,7 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23256,7 +23260,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23276,10 +23280,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23302,7 +23306,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23355,7 +23359,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23375,10 +23379,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23401,7 +23405,7 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23454,7 +23458,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -23474,10 +23478,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23500,7 +23504,7 @@
         <v>74</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23553,7 +23557,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -23573,10 +23577,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23599,7 +23603,7 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23652,7 +23656,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
